--- a/docs/triton-learning/cards/triton-lesson-05-layer-norm-correction.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-05-layer-norm-correction.xlsx
@@ -41,17 +41,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">为逐行 load/store 选择正确 mask</t>
+          <t xml:space="preserve">为逐行 LayerNorm 的读取和写回，判断当前行的哪些列有效。</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">一个 program 处理一行，cols 是行内列号</t>
+          <t xml:space="preserve">输入按行优先布局看成 \[M,N\]，M 是行数、N 是每行列数；一个 program 处理第 row 行，cols 表示它生成的行内列号。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">使用 cols &lt; N；再以 row*N+cols 形成线性地址。</t>
+          <t xml:space="preserve">使用 cols&lt;N 判断本行有效列，再用 row×N+cols 形成线性地址。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -61,27 +61,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：M 是行数，N 才是当前行的有效列数。
-• [T#B#总元素边界]：只检查线性地址小于 M*N，可能把下一行开头误当成本行尾部。
-• [T#B#尾部]：N=131、块长64时末轮从128开始，有效列为128、129、130。
-[T#B,!c47f17#边界]：地址在整个 tensor 内合法，不等于属于当前 program 的归约域。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：归一化域是当前这一行的 N 列，因此边界应比较行内列号与 N，不能比较行数 M，也不能只检查整个 tensor 的总元素数。
+• [T#B#为何总边界不够]：例如 M=5、N=3，第 row=2 行生成 cols=\[0,1,2,3\]，线性地址是 \[6,7,8,9\]。地址 9 仍在整个 tensor 内，却已属于下一行，不能参与当前行的统计量。
+• [T#B#正确结果]：上述 mask 应为 \[真,真,真,假\]，只读取地址 \[6,7,8\]。对于更宽行 N=131、块长 64，末轮从列 128 开始，有效列是 128、129、130，共 3 列。
+[T#B,!c47f17#边界]：地址在 tensor 内合法，与地址属于当前 program 的归一化行，是两个不同条件。边界必须同时保护内存安全和归约域正确性。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">解释 release 前的 tl.debug_barrier</t>
+          <t xml:space="preserve">解释更新共享梯度向量后，为什么要在 release 解锁前执行 tl.debug_barrier()。</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">一个 program 的多个线程共同写共享向量</t>
+          <t xml:space="preserve">一个 Triton program 的多个协作线程各自更新共享梯度槽的一部分，随后由执行到解锁指令的线程释放组锁，让下一个 program 使用完整更新。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrier 等待所有协作线程汇合；即使明确由T0解锁也需要它。</t>
+          <t xml:space="preserve">Barrier 让本 program 的协作线程先汇合，防止某个线程提前解锁；即使明确由线程 T0 解锁，也仍需保证其他线程已经完成各自的写入。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -91,9 +91,10 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：T0 走到解锁位置时，T1 仍可能没完成自己的写入。
-• [T#B#分工]：barrier 解决当前 block 内协作完成；release/acquire 解决下一个 program 的数据交接。
-[T#B,!c47f17#边界]：不是“任意线程完成 store 就自动触发解锁”；解锁仍是一条被执行到的指令。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：需要 barrier 的原因是协作写入可能尚未全部完成，而不是不知道谁负责解锁。知道解锁线程的身份，并不能让其他线程自动跟上它的进度。
+• [T#B#具体竞争]：假设明确由 T0 解锁。当 T0 写完自己负责的向量分片并走到解锁位置时，T1 仍可能在处理另一分片；若此刻释放锁，下一个 program 可能过早开始使用这个共享槽。
+• [T#B#正确分工]：block barrier 先让当前 program 内的协作线程汇合；随后的 release 与下一个 program 的 acquire，再负责跨 program 的受保护数据交接。
+[T#B,!c47f17#边界]：不是“某个线程一完成 store，就自动触发解锁”。解锁本身是一条按执行路径运行的指令，必须安排在必要的块内同步之后。</t>
         </is>
       </c>
     </row>

--- a/docs/triton-learning/cards/triton-lesson-05-layer-norm-correction.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-05-layer-norm-correction.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -41,17 +41,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">为逐行 LayerNorm 的读取和写回，判断当前行的哪些列有效。</t>
+          <t xml:space="preserve">为逐行 LayerNorm 的 load/store 写出只覆盖当前行有效元素的 mask。</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">输入按行优先布局看成 \[M,N\]，M 是行数、N 是每行列数；一个 program 处理第 row 行，cols 表示它生成的行内列号。</t>
+          <t xml:space="preserve">输入按行优先布局看成 \[M,N\]（M 行，每行 N 列）。一个 program 处理第 row 行：cols=tl.arange(0,BLOCK)，读写地址 offsets=row×N+cols，且 BLOCK≥N。原代码用 offsets&lt;M×N 作 mask。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">使用 cols&lt;N 判断本行有效列，再用 row×N+cols 形成线性地址。</t>
+          <t xml:space="preserve">mask=cols&lt;N：拿本行列号 cols 与每行列数 N 比较；读写地址仍是 row×N+cols。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -61,40 +61,70 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：归一化域是当前这一行的 N 列，因此边界应比较行内列号与 N，不能比较行数 M，也不能只检查整个 tensor 的总元素数。
-• [T#B#为何总边界不够]：例如 M=5、N=3，第 row=2 行生成 cols=\[0,1,2,3\]，线性地址是 \[6,7,8,9\]。地址 9 仍在整个 tensor 内，却已属于下一行，不能参与当前行的统计量。
-• [T#B#正确结果]：上述 mask 应为 \[真,真,真,假\]，只读取地址 \[6,7,8\]。对于更宽行 N=131、块长 64，末轮从列 128 开始，有效列是 128、129、130，共 3 列。
-[T#B,!c47f17#边界]：地址在 tensor 内合法，与地址属于当前 program 的归一化行，是两个不同条件。边界必须同时保护内存安全和归约域正确性。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：原答已正确发现 offsets&lt;M×N 只挡住整个 tensor 的末尾、会混入下一行；错在改法：M 是行数，offsets 是整个 tensor 的线性偏移，两者不能比较。归一化域是当前行的 N 列，所以要拿列号 cols 与 N 比较。
+• [T#B#为何总边界不够]：例如 M=5、N=3、BLOCK=4，第 row=2 行的 offsets=\[6,7,8,9\]。地址 9 小于 M×N=15，仍在 tensor 内，却属于下一行，会混入当前行的统计量。
+• [T#B#正确结果]：cols&lt;N 得到 \[真,真,真,假\]，只读写地址 \[6,7,8\]。
+[T#B,!c47f17#边界]：地址在 tensor 内合法，与地址属于当前 program 的归一化行，是两个不同条件；mask 必须同时保护内存安全和归约域正确性。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">解释更新共享梯度向量后，为什么要在 release 解锁前执行 tl.debug_barrier()。</t>
+          <t xml:space="preserve">解释：A 已执行写 buffer 的 store，B 随后读 buffer，为什么仍可能读到旧值？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">一个 Triton program 的多个协作线程各自更新共享梯度槽的一部分，随后由执行到解锁指令的线程释放组锁，让下一个 program 使用完整更新。</t>
+          <t xml:space="preserve">两个 Triton program 交接 buffer：A 写 buffer=42，再用 relaxed 原子操作解锁；B 的 relaxed CAS 拿到锁后读 buffer，没有其他同步。这里要说明旧值从哪来，而不是锁协议该怎么改。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barrier 让本 program 的协作线程先汇合，防止某个线程提前解锁；即使明确由线程 T0 解锁，也仍需保证其他线程已经完成各自的写入。</t>
+          <t xml:space="preserve">普通 load/store 不是需要专门等待完成的显式异步操作；B 读到旧值，是因为没有同步关系约束它看到哪个版本：访问可能被重排、重叠或命中旧缓存，已经完成的 load 也可能返回旧值。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">而我们无法确定是哪个线程负责解锁，所以需要barrier。</t>
+          <t xml:space="preserve">store和load这些操作本质上是异步的，仅发出读取和写入的指令。该条代码执行完成还不能保证读取和写入动作的完成。</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：需要 barrier 的原因是协作写入可能尚未全部完成，而不是不知道谁负责解锁。知道解锁线程的身份，并不能让其他线程自动跟上它的进度。
-• [T#B#具体竞争]：假设明确由 T0 解锁。当 T0 写完自己负责的向量分片并走到解锁位置时，T1 仍可能在处理另一分片；若此刻释放锁，下一个 program 可能过早开始使用这个共享槽。
-• [T#B#正确分工]：block barrier 先让当前 program 内的协作线程汇合；随后的 release 与下一个 program 的 acquire，再负责跨 program 的受保护数据交接。
-[T#B,!c47f17#边界]：不是“某个线程一完成 store，就自动触发解锁”。解锁本身是一条按执行路径运行的指令，必须安排在必要的块内同步之后。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：原答后半段（跨 program 需要 acquire+release 的同步锁，relaxed 锁无法确保这种同步关系）是对的；错在把读到旧值归因于 load/store “异步、尚未完成”。问题不在读写有没有完成，而在没有同步关系规定 B 能看到哪个版本。
+• [T#B#数据依赖保证什么]：v=tl.load(ptr)；y=v+1 中，编译器和硬件保证拿到 v 之后才计算 y，但不保证 v 是另一个 program 刚写入的版本。
+• [T#B#怎样交接]：跨 program 要建立顺序与可见性：用 release/acquire 的锁交接，或依靠同一 stream 中前后两个 kernel 的执行边界——第二阶段归约 kernel 读部分和不需要锁，靠的就是后者。
+[T#B,!c47f17#边界]：普通访问可以流水化、存在在途请求，但不应等同于需要专门等待完成的显式异步操作。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">若已规定由线程 T0 执行解锁，共享梯度槽解锁前的 tl.debug_barrier() 能省掉吗？为什么？</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triton LayerNorm 反向的共享梯度槽：持锁后用 tl.store 写组槽 → tl.debug_barrier() → tl.atomic_xchg 解锁；下一个 program 随后获锁读取该槽。</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不能省：即使已知由 T0 解锁，同一 program 的其他线程可能还没写完各自的分片；barrier 让所有协作线程先汇合，再解锁。</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">而我们无法确定是哪个线程负责解锁，所以需要barrier。</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：原答前半句对：解锁由某个线程执行，它先走到就可能提前解锁。错在归因：需要 barrier 是因为协作写入可能尚未全部完成，与是否知道谁解锁无关。
+• [T#B#具体竞争]：一行 tl.store 由本 program 的多个线程分片执行。假设由 T0 解锁：T0 写完自己的分片走到解锁位置时，T1 可能还在写另一分片；此刻释放锁，下一个 program 可能读到不完整的槽。
+• [T#B#正确分工]：block barrier 先让当前 program 内的协作线程汇合；随后的 release 与下一个 program 的 acquire，再负责跨 program 的数据交接。
+[T#B,!c47f17#边界]：解锁不是“某个线程一完成 store 就自动触发”，而是一条按执行路径运行的指令；它必须排在块内同步之后。</t>
         </is>
       </c>
     </row>
